--- a/input/reg_health_wellbeing.xlsx
+++ b/input/reg_health_wellbeing.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\andy_local\SimPaths project files\SimPaths\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2219F698-D79E-4541-A4E7-A159D929903F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04D26B29-1931-46E6-A34C-3E7BD5442906}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30" yWindow="2340" windowWidth="28770" windowHeight="13200" firstSheet="3" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UK_DHE_MCS1" sheetId="19" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="47">
   <si>
     <t>REGRESSOR</t>
   </si>
@@ -154,6 +154,21 @@
   </si>
   <si>
     <t>RealIncomeDecrease_D</t>
+  </si>
+  <si>
+    <t>D_Econ_benefits_UC_Lhw_ZERO</t>
+  </si>
+  <si>
+    <t>D_Econ_benefits_UC_Lhw_TEN</t>
+  </si>
+  <si>
+    <t>D_Econ_benefits_UC_Lhw_TWENTY</t>
+  </si>
+  <si>
+    <t>D_Econ_benefits_UC_Lhw_THIRTY</t>
+  </si>
+  <si>
+    <t>D_Econ_benefits_UC_Lhw_FORTY</t>
   </si>
 </sst>
 </file>
@@ -3351,13 +3366,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{832F923C-A72E-4542-A215-4DEB3BB7E81E}">
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3388,8 +3403,23 @@
       <c r="J1" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L1" t="s">
+        <v>43</v>
+      </c>
+      <c r="M1" t="s">
+        <v>44</v>
+      </c>
+      <c r="N1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>34</v>
       </c>
@@ -3420,8 +3450,23 @@
       <c r="J2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>35</v>
       </c>
@@ -3452,8 +3497,23 @@
       <c r="J3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>36</v>
       </c>
@@ -3484,8 +3544,23 @@
       <c r="J4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>37</v>
       </c>
@@ -3516,8 +3591,23 @@
       <c r="J5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>38</v>
       </c>
@@ -3548,8 +3638,23 @@
       <c r="J6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>39</v>
       </c>
@@ -3580,8 +3685,23 @@
       <c r="J7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>40</v>
       </c>
@@ -3612,8 +3732,23 @@
       <c r="J8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>41</v>
       </c>
@@ -3643,6 +3778,256 @@
       </c>
       <c r="J9">
         <v>1.30250079019638E-2</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10">
+        <v>-2.2400000000000002</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>9.0920710120782997E-2</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11">
+        <v>-1.27</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>0.40933881715951598</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12">
+        <v>-1.0740000000000001</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0.23123340535193601</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13">
+        <v>-0.55900000000000005</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0.22708142440649701</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B14">
+        <v>-0.76900000000000002</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0.140625</v>
       </c>
     </row>
   </sheetData>
@@ -3653,13 +4038,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{507D7AC2-8D5E-4487-A269-96C4EFD731AD}">
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3690,8 +4075,23 @@
       <c r="J1" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L1" t="s">
+        <v>43</v>
+      </c>
+      <c r="M1" t="s">
+        <v>44</v>
+      </c>
+      <c r="N1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>34</v>
       </c>
@@ -3722,8 +4122,23 @@
       <c r="J2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>35</v>
       </c>
@@ -3754,8 +4169,23 @@
       <c r="J3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>36</v>
       </c>
@@ -3786,8 +4216,23 @@
       <c r="J4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>37</v>
       </c>
@@ -3818,8 +4263,23 @@
       <c r="J5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>38</v>
       </c>
@@ -3850,8 +4310,23 @@
       <c r="J6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>39</v>
       </c>
@@ -3882,8 +4357,23 @@
       <c r="J7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>40</v>
       </c>
@@ -3914,8 +4404,23 @@
       <c r="J8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>41</v>
       </c>
@@ -3945,6 +4450,256 @@
       </c>
       <c r="J9">
         <v>1.3002974181362301E-2</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10">
+        <v>-2.2400000000000002</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>9.0920710120782997E-2</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11">
+        <v>-1.27</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>0.40933881715951598</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12">
+        <v>-1.0740000000000001</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0.23123340535193601</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13">
+        <v>-0.55900000000000005</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0.22708142440649701</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B14">
+        <v>-0.76900000000000002</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0.140625</v>
       </c>
     </row>
   </sheetData>

--- a/input/reg_health_wellbeing.xlsx
+++ b/input/reg_health_wellbeing.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\andy_local\SimPaths project files\SimPaths\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04D26B29-1931-46E6-A34C-3E7BD5442906}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB080870-90F7-4EF9-9C15-1459D03617A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UK_DHE_MCS1" sheetId="19" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="48">
   <si>
     <t>REGRESSOR</t>
   </si>
@@ -169,6 +169,9 @@
   </si>
   <si>
     <t>D_Econ_benefits_UC_Lhw_FORTY</t>
+  </si>
+  <si>
+    <t>D_Econ_benefits_UC</t>
   </si>
 </sst>
 </file>
@@ -3366,13 +3369,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{832F923C-A72E-4542-A215-4DEB3BB7E81E}">
-  <dimension ref="A1:O14"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3418,8 +3421,11 @@
       <c r="O1" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>34</v>
       </c>
@@ -3465,8 +3471,11 @@
       <c r="O2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>35</v>
       </c>
@@ -3512,8 +3521,11 @@
       <c r="O3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>36</v>
       </c>
@@ -3559,8 +3571,11 @@
       <c r="O4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>37</v>
       </c>
@@ -3606,8 +3621,11 @@
       <c r="O5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>38</v>
       </c>
@@ -3653,8 +3671,11 @@
       <c r="O6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>39</v>
       </c>
@@ -3700,8 +3721,11 @@
       <c r="O7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>40</v>
       </c>
@@ -3747,8 +3771,11 @@
       <c r="O8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>41</v>
       </c>
@@ -3794,8 +3821,11 @@
       <c r="O9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>42</v>
       </c>
@@ -3841,8 +3871,11 @@
       <c r="O10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>43</v>
       </c>
@@ -3888,8 +3921,11 @@
       <c r="O11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>44</v>
       </c>
@@ -3935,8 +3971,11 @@
       <c r="O12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>45</v>
       </c>
@@ -3982,8 +4021,11 @@
       <c r="O13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>46</v>
       </c>
@@ -4028,6 +4070,59 @@
       </c>
       <c r="O14">
         <v>0.140625</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>47</v>
+      </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4038,13 +4133,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{507D7AC2-8D5E-4487-A269-96C4EFD731AD}">
-  <dimension ref="A1:O14"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4090,8 +4185,11 @@
       <c r="O1" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>34</v>
       </c>
@@ -4137,8 +4235,11 @@
       <c r="O2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>35</v>
       </c>
@@ -4184,8 +4285,11 @@
       <c r="O3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>36</v>
       </c>
@@ -4231,8 +4335,11 @@
       <c r="O4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>37</v>
       </c>
@@ -4278,8 +4385,11 @@
       <c r="O5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>38</v>
       </c>
@@ -4325,8 +4435,11 @@
       <c r="O6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>39</v>
       </c>
@@ -4372,8 +4485,11 @@
       <c r="O7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>40</v>
       </c>
@@ -4419,8 +4535,11 @@
       <c r="O8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>41</v>
       </c>
@@ -4466,8 +4585,11 @@
       <c r="O9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>42</v>
       </c>
@@ -4513,8 +4635,11 @@
       <c r="O10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>43</v>
       </c>
@@ -4560,8 +4685,11 @@
       <c r="O11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>44</v>
       </c>
@@ -4607,8 +4735,11 @@
       <c r="O12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>45</v>
       </c>
@@ -4654,8 +4785,11 @@
       <c r="O13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>46</v>
       </c>
@@ -4700,6 +4834,59 @@
       </c>
       <c r="O14">
         <v>0.140625</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>47</v>
+      </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -7574,13 +7761,13 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61FFD135-F68D-4BA5-8428-237AEC5FBCBF}">
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7611,8 +7798,26 @@
       <c r="J1" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L1" t="s">
+        <v>43</v>
+      </c>
+      <c r="M1" t="s">
+        <v>44</v>
+      </c>
+      <c r="N1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" t="s">
+        <v>46</v>
+      </c>
+      <c r="P1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>34</v>
       </c>
@@ -7643,8 +7848,26 @@
       <c r="J2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>35</v>
       </c>
@@ -7675,8 +7898,26 @@
       <c r="J3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>36</v>
       </c>
@@ -7707,8 +7948,26 @@
       <c r="J4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>37</v>
       </c>
@@ -7739,8 +7998,26 @@
       <c r="J5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>38</v>
       </c>
@@ -7771,8 +8048,26 @@
       <c r="J6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>39</v>
       </c>
@@ -7803,8 +8098,26 @@
       <c r="J7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>40</v>
       </c>
@@ -7835,8 +8148,26 @@
       <c r="J8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>41</v>
       </c>
@@ -7866,6 +8197,324 @@
       </c>
       <c r="J9">
         <v>8.7341353533867492E-3</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>47</v>
+      </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -7876,13 +8525,13 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF31F872-D261-41D6-B2CC-193676928E50}">
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7913,8 +8562,26 @@
       <c r="J1" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L1" t="s">
+        <v>43</v>
+      </c>
+      <c r="M1" t="s">
+        <v>44</v>
+      </c>
+      <c r="N1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" t="s">
+        <v>46</v>
+      </c>
+      <c r="P1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>34</v>
       </c>
@@ -7945,8 +8612,26 @@
       <c r="J2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>35</v>
       </c>
@@ -7977,8 +8662,26 @@
       <c r="J3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>36</v>
       </c>
@@ -8009,8 +8712,26 @@
       <c r="J4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>37</v>
       </c>
@@ -8041,8 +8762,26 @@
       <c r="J5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>38</v>
       </c>
@@ -8073,8 +8812,26 @@
       <c r="J6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>39</v>
       </c>
@@ -8105,8 +8862,26 @@
       <c r="J7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>40</v>
       </c>
@@ -8137,8 +8912,26 @@
       <c r="J8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>41</v>
       </c>
@@ -8168,6 +8961,324 @@
       </c>
       <c r="J9">
         <v>7.9152184076762208E-3</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>47</v>
+      </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -11042,13 +12153,13 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5133760B-11D7-4829-93B2-89ABD9DB533E}">
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -11079,8 +12190,26 @@
       <c r="J1" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L1" t="s">
+        <v>43</v>
+      </c>
+      <c r="M1" t="s">
+        <v>44</v>
+      </c>
+      <c r="N1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" t="s">
+        <v>46</v>
+      </c>
+      <c r="P1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>34</v>
       </c>
@@ -11111,8 +12240,26 @@
       <c r="J2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>35</v>
       </c>
@@ -11143,8 +12290,26 @@
       <c r="J3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>36</v>
       </c>
@@ -11175,8 +12340,26 @@
       <c r="J4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>37</v>
       </c>
@@ -11207,8 +12390,26 @@
       <c r="J5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>38</v>
       </c>
@@ -11239,8 +12440,26 @@
       <c r="J6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>39</v>
       </c>
@@ -11271,8 +12490,26 @@
       <c r="J7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>40</v>
       </c>
@@ -11303,8 +12540,26 @@
       <c r="J8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>41</v>
       </c>
@@ -11334,6 +12589,324 @@
       </c>
       <c r="J9">
         <v>3.6874115022289701E-4</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>47</v>
+      </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -11344,13 +12917,13 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E3469CB-42ED-4984-ACB1-66223A508A16}">
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -11381,8 +12954,26 @@
       <c r="J1" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L1" t="s">
+        <v>43</v>
+      </c>
+      <c r="M1" t="s">
+        <v>44</v>
+      </c>
+      <c r="N1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" t="s">
+        <v>46</v>
+      </c>
+      <c r="P1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>34</v>
       </c>
@@ -11413,8 +13004,26 @@
       <c r="J2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>35</v>
       </c>
@@ -11445,8 +13054,26 @@
       <c r="J3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>36</v>
       </c>
@@ -11477,8 +13104,26 @@
       <c r="J4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>37</v>
       </c>
@@ -11509,8 +13154,26 @@
       <c r="J5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>38</v>
       </c>
@@ -11541,8 +13204,26 @@
       <c r="J6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>39</v>
       </c>
@@ -11573,8 +13254,26 @@
       <c r="J7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>40</v>
       </c>
@@ -11605,8 +13304,26 @@
       <c r="J8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>41</v>
       </c>
@@ -11636,6 +13353,324 @@
       </c>
       <c r="J9">
         <v>2.8798836850867597E-4</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>47</v>
+      </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/input/reg_health_wellbeing.xlsx
+++ b/input/reg_health_wellbeing.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\andy_local\SimPaths project files\SimPaths\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB080870-90F7-4EF9-9C15-1459D03617A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3BFA8EC-CB4B-4424-8B04-9A8EF86366EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UK_DHE_MCS1" sheetId="19" r:id="rId1"/>
@@ -23,7 +23,20 @@
     <sheet name="UK_DLS2_Males" sheetId="17" r:id="rId8"/>
     <sheet name="UK_DLS2_Females" sheetId="18" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -3830,7 +3843,7 @@
         <v>42</v>
       </c>
       <c r="B10">
-        <v>-2.2400000000000002</v>
+        <v>0</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -3857,7 +3870,7 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>9.0920710120782997E-2</v>
+        <v>0</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -3880,7 +3893,7 @@
         <v>43</v>
       </c>
       <c r="B11">
-        <v>-1.27</v>
+        <v>0</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -3910,7 +3923,7 @@
         <v>0</v>
       </c>
       <c r="L11">
-        <v>0.40933881715951598</v>
+        <v>0</v>
       </c>
       <c r="M11">
         <v>0</v>
@@ -3930,7 +3943,7 @@
         <v>44</v>
       </c>
       <c r="B12">
-        <v>-1.0740000000000001</v>
+        <v>0</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -3963,7 +3976,7 @@
         <v>0</v>
       </c>
       <c r="M12">
-        <v>0.23123340535193601</v>
+        <v>0</v>
       </c>
       <c r="N12">
         <v>0</v>
@@ -3980,7 +3993,7 @@
         <v>45</v>
       </c>
       <c r="B13">
-        <v>-0.55900000000000005</v>
+        <v>0</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -4016,7 +4029,7 @@
         <v>0</v>
       </c>
       <c r="N13">
-        <v>0.22708142440649701</v>
+        <v>0</v>
       </c>
       <c r="O13">
         <v>0</v>
@@ -4030,7 +4043,7 @@
         <v>46</v>
       </c>
       <c r="B14">
-        <v>-0.76900000000000002</v>
+        <v>0</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -4069,7 +4082,7 @@
         <v>0</v>
       </c>
       <c r="O14">
-        <v>0.140625</v>
+        <v>0</v>
       </c>
       <c r="P14">
         <v>0</v>
@@ -4080,7 +4093,7 @@
         <v>47</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>-0.69799999999999995</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -4122,7 +4135,7 @@
         <v>0</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>7.7284000000000019E-2</v>
       </c>
     </row>
   </sheetData>
@@ -4594,7 +4607,7 @@
         <v>42</v>
       </c>
       <c r="B10">
-        <v>-2.2400000000000002</v>
+        <v>0</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -4621,7 +4634,7 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>9.0920710120782997E-2</v>
+        <v>0</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -4644,7 +4657,7 @@
         <v>43</v>
       </c>
       <c r="B11">
-        <v>-1.27</v>
+        <v>0</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -4674,7 +4687,7 @@
         <v>0</v>
       </c>
       <c r="L11">
-        <v>0.40933881715951598</v>
+        <v>0</v>
       </c>
       <c r="M11">
         <v>0</v>
@@ -4694,7 +4707,7 @@
         <v>44</v>
       </c>
       <c r="B12">
-        <v>-1.0740000000000001</v>
+        <v>0</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -4727,7 +4740,7 @@
         <v>0</v>
       </c>
       <c r="M12">
-        <v>0.23123340535193601</v>
+        <v>0</v>
       </c>
       <c r="N12">
         <v>0</v>
@@ -4744,7 +4757,7 @@
         <v>45</v>
       </c>
       <c r="B13">
-        <v>-0.55900000000000005</v>
+        <v>0</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -4780,7 +4793,7 @@
         <v>0</v>
       </c>
       <c r="N13">
-        <v>0.22708142440649701</v>
+        <v>0</v>
       </c>
       <c r="O13">
         <v>0</v>
@@ -4794,7 +4807,7 @@
         <v>46</v>
       </c>
       <c r="B14">
-        <v>-0.76900000000000002</v>
+        <v>0</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -4833,7 +4846,7 @@
         <v>0</v>
       </c>
       <c r="O14">
-        <v>0.140625</v>
+        <v>0</v>
       </c>
       <c r="P14">
         <v>0</v>
@@ -4844,7 +4857,7 @@
         <v>47</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>-0.69799999999999995</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -4886,7 +4899,7 @@
         <v>0</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>7.7284000000000019E-2</v>
       </c>
     </row>
   </sheetData>
@@ -8472,7 +8485,7 @@
         <v>47</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>-0.23599999999999999</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -8514,7 +8527,7 @@
         <v>0</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>4.5795999999999996E-2</v>
       </c>
     </row>
   </sheetData>
@@ -9236,7 +9249,7 @@
         <v>47</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>-0.23599999999999999</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -9278,7 +9291,7 @@
         <v>0</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>4.5795999999999996E-2</v>
       </c>
     </row>
   </sheetData>
@@ -12864,7 +12877,7 @@
         <v>47</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>-0.45797872340425538</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -12906,12 +12919,12 @@
         <v>0</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>1.6215583974649166E-2</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -13628,7 +13641,7 @@
         <v>47</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>-0.45797872340425538</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -13670,7 +13683,7 @@
         <v>0</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>1.6215583974649166E-2</v>
       </c>
     </row>
   </sheetData>

--- a/input/reg_health_wellbeing.xlsx
+++ b/input/reg_health_wellbeing.xlsx
@@ -1,28 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\andy_local\SimPaths project files\SimPaths\input\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Sonnewald/GitHub/SimPaths/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B698CB95-923A-4345-BDDC-5EBAC21A34E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BBD6F00-F9A7-FD47-87ED-88F907BE8979}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17800" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="10" r:id="rId1"/>
-    <sheet name="UK_DHE_MCS1" sheetId="11" r:id="rId2"/>
-    <sheet name="UK_DHE_MCS2_Females" sheetId="12" r:id="rId3"/>
-    <sheet name="UK_DHE_MCS2_Males" sheetId="13" r:id="rId4"/>
-    <sheet name="UK_DHE_PCS1" sheetId="14" r:id="rId5"/>
-    <sheet name="UK_DHE_PCS2_Females" sheetId="15" r:id="rId6"/>
-    <sheet name="UK_DHE_PCS2_Males" sheetId="16" r:id="rId7"/>
-    <sheet name="UK_DLS1" sheetId="17" r:id="rId8"/>
-    <sheet name="UK_DLS2_Females" sheetId="18" r:id="rId9"/>
-    <sheet name="UK_DLS2_Males" sheetId="19" r:id="rId10"/>
+    <sheet name="DHE_MCS1" sheetId="11" r:id="rId2"/>
+    <sheet name="DHE_MCS2_Females" sheetId="12" r:id="rId3"/>
+    <sheet name="DHE_MCS2_Males" sheetId="13" r:id="rId4"/>
+    <sheet name="DHE_PCS1" sheetId="14" r:id="rId5"/>
+    <sheet name="DHE_PCS2_Females" sheetId="15" r:id="rId6"/>
+    <sheet name="DHE_PCS2_Males" sheetId="16" r:id="rId7"/>
+    <sheet name="DLS1" sheetId="17" r:id="rId8"/>
+    <sheet name="DLS2_Females" sheetId="18" r:id="rId9"/>
+    <sheet name="DLS2_Males" sheetId="19" r:id="rId10"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -178,6 +178,7 @@
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -548,7 +549,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FDA0D7D-330C-4038-8F65-88620937F5B8}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -557,12 +558,12 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11572986-38C7-4EDA-A20B-58ABE51A5256}">
   <dimension ref="A1:M12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="16384" width="9.1640625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -603,7 +604,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>33</v>
       </c>
@@ -644,7 +645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>34</v>
       </c>
@@ -685,7 +686,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>35</v>
       </c>
@@ -726,7 +727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>36</v>
       </c>
@@ -767,7 +768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>37</v>
       </c>
@@ -808,7 +809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>38</v>
       </c>
@@ -849,7 +850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>39</v>
       </c>
@@ -890,7 +891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>40</v>
       </c>
@@ -931,7 +932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>41</v>
       </c>
@@ -972,7 +973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>43</v>
       </c>
@@ -1013,7 +1014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>44</v>
       </c>
@@ -1062,12 +1063,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86B3B5C4-1A53-48E7-858C-54671C86726A}">
   <dimension ref="A1:AG32"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="16384" width="9.1640625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1168,7 +1169,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -1269,7 +1270,7 @@
         <v>-1.7453704807669703E-4</v>
       </c>
     </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -1370,7 +1371,7 @@
         <v>-4.3152426714815426E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -1471,7 +1472,7 @@
         <v>-1.1168720109462238E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -1572,7 +1573,7 @@
         <v>-2.4476810261714457E-4</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
@@ -1673,7 +1674,7 @@
         <v>-5.4206455823061044E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
@@ -1774,7 +1775,7 @@
         <v>-5.2278141390579022E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
@@ -1875,7 +1876,7 @@
         <v>-5.2879150435504816E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
@@ -1976,7 +1977,7 @@
         <v>-4.9191904134959288E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
@@ -2077,7 +2078,7 @@
         <v>-4.9640796352598158E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
@@ -2178,7 +2179,7 @@
         <v>-4.8736954785940974E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
@@ -2279,7 +2280,7 @@
         <v>-5.2162678557267188E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
@@ -2380,7 +2381,7 @@
         <v>-4.6793547668442506E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
@@ -2481,7 +2482,7 @@
         <v>-5.9216934221460607E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>14</v>
       </c>
@@ -2582,7 +2583,7 @@
         <v>-4.998546055291854E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>15</v>
       </c>
@@ -2683,7 +2684,7 @@
         <v>-5.4279322260864151E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>16</v>
       </c>
@@ -2784,7 +2785,7 @@
         <v>-2.5528733863520846E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>17</v>
       </c>
@@ -2885,7 +2886,7 @@
         <v>-1.9899947674301187E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>18</v>
       </c>
@@ -2986,7 +2987,7 @@
         <v>-1.5880856738040919E-3</v>
       </c>
     </row>
-    <row r="20" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>19</v>
       </c>
@@ -3087,7 +3088,7 @@
         <v>-2.0035773826385826E-3</v>
       </c>
     </row>
-    <row r="21" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>20</v>
       </c>
@@ -3188,7 +3189,7 @@
         <v>-6.3817282824218773E-3</v>
       </c>
     </row>
-    <row r="22" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>21</v>
       </c>
@@ -3289,7 +3290,7 @@
         <v>-3.7317463164202166E-4</v>
       </c>
     </row>
-    <row r="23" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>22</v>
       </c>
@@ -3390,7 +3391,7 @@
         <v>-8.0843632267291665E-4</v>
       </c>
     </row>
-    <row r="24" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>23</v>
       </c>
@@ -3491,7 +3492,7 @@
         <v>7.0800831782135641E-6</v>
       </c>
     </row>
-    <row r="25" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>24</v>
       </c>
@@ -3592,7 +3593,7 @@
         <v>-2.1366033660005432E-3</v>
       </c>
     </row>
-    <row r="26" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>25</v>
       </c>
@@ -3693,7 +3694,7 @@
         <v>-3.1716699461619147E-3</v>
       </c>
     </row>
-    <row r="27" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>26</v>
       </c>
@@ -3794,7 +3795,7 @@
         <v>-3.2550952540028408E-3</v>
       </c>
     </row>
-    <row r="28" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>27</v>
       </c>
@@ -3895,7 +3896,7 @@
         <v>-3.5366665094436951E-3</v>
       </c>
     </row>
-    <row r="29" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>28</v>
       </c>
@@ -3996,7 +3997,7 @@
         <v>-3.6874245480089302E-3</v>
       </c>
     </row>
-    <row r="30" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>29</v>
       </c>
@@ -4097,7 +4098,7 @@
         <v>-1.3682859083442801E-4</v>
       </c>
     </row>
-    <row r="31" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>30</v>
       </c>
@@ -4198,7 +4199,7 @@
         <v>-2.9836643810171744E-4</v>
       </c>
     </row>
-    <row r="32" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>31</v>
       </c>
@@ -4307,12 +4308,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{815F9260-CCEF-41E5-95CB-A3793F4D911F}">
   <dimension ref="A1:M12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="16384" width="9.1640625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4353,7 +4354,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>33</v>
       </c>
@@ -4394,7 +4395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>34</v>
       </c>
@@ -4435,7 +4436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>35</v>
       </c>
@@ -4476,7 +4477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>36</v>
       </c>
@@ -4517,7 +4518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>37</v>
       </c>
@@ -4558,7 +4559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>38</v>
       </c>
@@ -4599,7 +4600,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>39</v>
       </c>
@@ -4640,7 +4641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>40</v>
       </c>
@@ -4681,7 +4682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>41</v>
       </c>
@@ -4722,7 +4723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>43</v>
       </c>
@@ -4763,7 +4764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>44</v>
       </c>
@@ -4812,12 +4813,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E52CA595-EF5A-4B89-ADDA-26B507FA5B54}">
   <dimension ref="A1:M12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="16384" width="9.1640625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4858,7 +4859,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>33</v>
       </c>
@@ -4899,7 +4900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>34</v>
       </c>
@@ -4940,7 +4941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>35</v>
       </c>
@@ -4981,7 +4982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>36</v>
       </c>
@@ -5022,7 +5023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>37</v>
       </c>
@@ -5063,7 +5064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>38</v>
       </c>
@@ -5104,7 +5105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>39</v>
       </c>
@@ -5145,7 +5146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>40</v>
       </c>
@@ -5186,7 +5187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>41</v>
       </c>
@@ -5227,7 +5228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>43</v>
       </c>
@@ -5268,7 +5269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>44</v>
       </c>
@@ -5317,12 +5318,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2C5547B-AC4D-4D56-8052-0AF5A9C1CD39}">
   <dimension ref="A1:AG32"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="16384" width="9.1640625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5423,7 +5424,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -5524,7 +5525,7 @@
         <v>3.343829620811265E-4</v>
       </c>
     </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -5625,7 +5626,7 @@
         <v>-3.4043232644715505E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -5726,7 +5727,7 @@
         <v>-4.53002147207351E-4</v>
       </c>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>21</v>
       </c>
@@ -5827,7 +5828,7 @@
         <v>-1.9380770819514917E-4</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
@@ -5928,7 +5929,7 @@
         <v>-3.8259190906371606E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
@@ -6029,7 +6030,7 @@
         <v>-3.5271935407985419E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
@@ -6130,7 +6131,7 @@
         <v>-3.5780432769120752E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
@@ -6231,7 +6232,7 @@
         <v>-3.7584134662251101E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
@@ -6332,7 +6333,7 @@
         <v>-3.4994185737892642E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
@@ -6433,7 +6434,7 @@
         <v>-3.4747269327166999E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
@@ -6534,7 +6535,7 @@
         <v>-3.2858840401762688E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
@@ -6635,7 +6636,7 @@
         <v>-3.3761709406766056E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
@@ -6736,7 +6737,7 @@
         <v>-4.3929208970911911E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>14</v>
       </c>
@@ -6837,7 +6838,7 @@
         <v>-3.6635836456209454E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>15</v>
       </c>
@@ -6938,7 +6939,7 @@
         <v>-3.8884082736424753E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>16</v>
       </c>
@@ -7039,7 +7040,7 @@
         <v>-1.9936511529351133E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>17</v>
       </c>
@@ -7140,7 +7141,7 @@
         <v>-1.299769839066248E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>18</v>
       </c>
@@ -7241,7 +7242,7 @@
         <v>-1.0578377284416445E-3</v>
       </c>
     </row>
-    <row r="20" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>19</v>
       </c>
@@ -7342,7 +7343,7 @@
         <v>-1.3082554198197475E-3</v>
       </c>
     </row>
-    <row r="21" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>20</v>
       </c>
@@ -7443,7 +7444,7 @@
         <v>-7.1103946136907631E-3</v>
       </c>
     </row>
-    <row r="22" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>4</v>
       </c>
@@ -7544,7 +7545,7 @@
         <v>-3.842829404906051E-4</v>
       </c>
     </row>
-    <row r="23" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>22</v>
       </c>
@@ -7645,7 +7646,7 @@
         <v>-4.8708683559203509E-4</v>
       </c>
     </row>
-    <row r="24" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>23</v>
       </c>
@@ -7746,7 +7747,7 @@
         <v>4.0463495233332193E-6</v>
       </c>
     </row>
-    <row r="25" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>24</v>
       </c>
@@ -7847,7 +7848,7 @@
         <v>-1.910519474017742E-3</v>
       </c>
     </row>
-    <row r="26" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>25</v>
       </c>
@@ -7948,7 +7949,7 @@
         <v>-3.2284445712567958E-3</v>
       </c>
     </row>
-    <row r="27" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>26</v>
       </c>
@@ -8049,7 +8050,7 @@
         <v>-2.7008033460173232E-3</v>
       </c>
     </row>
-    <row r="28" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>27</v>
       </c>
@@ -8150,7 +8151,7 @@
         <v>-1.9537615899141401E-3</v>
       </c>
     </row>
-    <row r="29" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>28</v>
       </c>
@@ -8251,7 +8252,7 @@
         <v>-2.3472404999291077E-3</v>
       </c>
     </row>
-    <row r="30" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>29</v>
       </c>
@@ -8352,7 +8353,7 @@
         <v>-2.0112181389998567E-4</v>
       </c>
     </row>
-    <row r="31" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>30</v>
       </c>
@@ -8453,7 +8454,7 @@
         <v>-2.5807135896457477E-4</v>
       </c>
     </row>
-    <row r="32" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>31</v>
       </c>
@@ -8562,12 +8563,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9FA8D6C-9D41-4B83-96DC-3CE185883661}">
   <dimension ref="A1:M12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="16384" width="9.1640625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8608,7 +8609,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>33</v>
       </c>
@@ -8649,7 +8650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>34</v>
       </c>
@@ -8690,7 +8691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>35</v>
       </c>
@@ -8731,7 +8732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>36</v>
       </c>
@@ -8772,7 +8773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>37</v>
       </c>
@@ -8813,7 +8814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>38</v>
       </c>
@@ -8854,7 +8855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>39</v>
       </c>
@@ -8895,7 +8896,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>40</v>
       </c>
@@ -8936,7 +8937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>41</v>
       </c>
@@ -8977,7 +8978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>43</v>
       </c>
@@ -9018,7 +9019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>44</v>
       </c>
@@ -9067,12 +9068,12 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F90A3630-8F41-4CB5-B1DE-F906AA02BA4D}">
   <dimension ref="A1:M12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="16384" width="9.1640625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9113,7 +9114,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>33</v>
       </c>
@@ -9154,7 +9155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>34</v>
       </c>
@@ -9195,7 +9196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>35</v>
       </c>
@@ -9236,7 +9237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>36</v>
       </c>
@@ -9277,7 +9278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>37</v>
       </c>
@@ -9318,7 +9319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>38</v>
       </c>
@@ -9359,7 +9360,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>39</v>
       </c>
@@ -9400,7 +9401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>40</v>
       </c>
@@ -9441,7 +9442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>41</v>
       </c>
@@ -9482,7 +9483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>43</v>
       </c>
@@ -9523,7 +9524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>44</v>
       </c>
@@ -9572,12 +9573,12 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90E38585-26C6-49B6-9374-490DD727B13C}">
   <dimension ref="A1:AG32"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="16384" width="9.1640625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9678,7 +9679,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -9779,7 +9780,7 @@
         <v>-1.0616661273375814E-5</v>
       </c>
     </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -9880,7 +9881,7 @@
         <v>-3.3290259184851664E-4</v>
       </c>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -9981,7 +9982,7 @@
         <v>-7.1599936326444672E-5</v>
       </c>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -10082,7 +10083,7 @@
         <v>-1.5657669177001639E-5</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
@@ -10183,7 +10184,7 @@
         <v>-4.0638375541948469E-4</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
@@ -10284,7 +10285,7 @@
         <v>-4.1290519348920413E-4</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
@@ -10385,7 +10386,7 @@
         <v>-4.0211132250117618E-4</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
@@ -10486,7 +10487,7 @@
         <v>-3.9493107488816257E-4</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
@@ -10587,7 +10588,7 @@
         <v>-3.8548510593851434E-4</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
@@ -10688,7 +10689,7 @@
         <v>-3.8267227744772975E-4</v>
       </c>
     </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
@@ -10789,7 +10790,7 @@
         <v>-4.0760555823028124E-4</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
@@ -10890,7 +10891,7 @@
         <v>-4.0543228575117658E-4</v>
       </c>
     </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
@@ -10991,7 +10992,7 @@
         <v>-4.3375172294051964E-4</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>14</v>
       </c>
@@ -11092,7 +11093,7 @@
         <v>-4.1027116808240192E-4</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>15</v>
       </c>
@@ -11193,7 +11194,7 @@
         <v>-4.1679373644655369E-4</v>
       </c>
     </row>
-    <row r="17" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>16</v>
       </c>
@@ -11294,7 +11295,7 @@
         <v>-1.9485882392709415E-4</v>
       </c>
     </row>
-    <row r="18" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>17</v>
       </c>
@@ -11395,7 +11396,7 @@
         <v>-1.7537536900790105E-4</v>
       </c>
     </row>
-    <row r="19" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>18</v>
       </c>
@@ -11496,7 +11497,7 @@
         <v>-1.6254007690859857E-4</v>
       </c>
     </row>
-    <row r="20" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>19</v>
       </c>
@@ -11597,7 +11598,7 @@
         <v>-1.8177404420396666E-4</v>
       </c>
     </row>
-    <row r="21" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>20</v>
       </c>
@@ -11698,7 +11699,7 @@
         <v>-3.1650747671789584E-4</v>
       </c>
     </row>
-    <row r="22" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>42</v>
       </c>
@@ -11799,7 +11800,7 @@
         <v>-6.0833175280594264E-5</v>
       </c>
     </row>
-    <row r="23" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>22</v>
       </c>
@@ -11900,7 +11901,7 @@
         <v>-5.7850239438462855E-5</v>
       </c>
     </row>
-    <row r="24" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>23</v>
       </c>
@@ -12001,7 +12002,7 @@
         <v>4.9211123641168937E-7</v>
       </c>
     </row>
-    <row r="25" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>24</v>
       </c>
@@ -12102,7 +12103,7 @@
         <v>-1.4904183827279822E-4</v>
       </c>
     </row>
-    <row r="26" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>25</v>
       </c>
@@ -12203,7 +12204,7 @@
         <v>-2.3077122398439153E-4</v>
       </c>
     </row>
-    <row r="27" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>26</v>
       </c>
@@ -12304,7 +12305,7 @@
         <v>-2.4331099274807098E-4</v>
       </c>
     </row>
-    <row r="28" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>27</v>
       </c>
@@ -12405,7 +12406,7 @@
         <v>-3.0744260223757719E-4</v>
       </c>
     </row>
-    <row r="29" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>28</v>
       </c>
@@ -12506,7 +12507,7 @@
         <v>-2.2501030415023098E-4</v>
       </c>
     </row>
-    <row r="30" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>29</v>
       </c>
@@ -12607,7 +12608,7 @@
         <v>-6.9758130845640412E-5</v>
       </c>
     </row>
-    <row r="31" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>30</v>
       </c>
@@ -12708,7 +12709,7 @@
         <v>-1.3188364418032388E-5</v>
       </c>
     </row>
-    <row r="32" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>31</v>
       </c>
@@ -12817,12 +12818,12 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8271DA1-113B-44D0-8CF2-767CF072D053}">
   <dimension ref="A1:M12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="16384" width="9.1640625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -12863,7 +12864,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>33</v>
       </c>
@@ -12904,7 +12905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>34</v>
       </c>
@@ -12945,7 +12946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>35</v>
       </c>
@@ -12986,7 +12987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>36</v>
       </c>
@@ -13027,7 +13028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>37</v>
       </c>
@@ -13068,7 +13069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>38</v>
       </c>
@@ -13109,7 +13110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>39</v>
       </c>
@@ -13150,7 +13151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>40</v>
       </c>
@@ -13191,7 +13192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>41</v>
       </c>
@@ -13232,7 +13233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>43</v>
       </c>
@@ -13273,7 +13274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>44</v>
       </c>
